--- a/financial_advisor_forms/014_financial_planner_recommendation_form--financial_advisor_forms.xlsx
+++ b/financial_advisor_forms/014_financial_planner_recommendation_form--financial_advisor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -531,7 +531,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -577,47 +577,47 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>date_of_birth</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Date Of Birth</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
+          <t>financial_institution</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Date of Birth</t>
+          <t>Financial Institution</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,40 +630,40 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>financial_institution</t>
+          <t>account_type</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Financial Institution</t>
+          <t>Account Type</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>account_type</t>
+          <t>asset_allocation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Account Type</t>
+          <t>Asset Allocation</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>asset_allocation</t>
+          <t>risk_tolerance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Asset Allocation</t>
+          <t>Risk Tolerance</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>risk_tolerance</t>
+          <t>investment_horizon</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Risk Tolerance</t>
+          <t>Investment Horizon</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>investment_horizon</t>
+          <t>asset_allocation_target</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Investment Horizon</t>
+          <t>Asset Allocation Target</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>asset_allocation_target</t>
+          <t>financial_goals</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Asset Allocation Target</t>
+          <t>Financial Goals</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,322 +768,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>financial_goals</t>
+          <t>investment_objects</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Financial Goals</t>
+          <t>Investment Objects</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>investment_objects</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Investment Objects</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>investment_horizon</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Investment Horizon</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>risk_free_rate</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Risk Free Rate</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>financial_institution</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Financial Institution</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>account_holder</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Account Holder</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>account_address</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Account Address</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>account_type</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Account Type</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>financial_institution</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Financial Institution</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>account_type</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Account Type</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>investment_horizon</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Investment Horizon</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>financial_institution</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Financial Institution</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>financial_institution</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Financial Institution</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>account_address</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Account Address</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
         </is>
       </c>
     </row>
